--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12947.67</v>
+        <v>12760.36</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45917.56</v>
+        <v>46307.26</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11109.43</v>
+        <v>11155.47</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>22536.93</v>
+        <v>22788.97</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6628.51</v>
+        <v>6677.89</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1667.6</v>
+        <v>1673.13</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26736.84</v>
+        <v>26821.94</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10750.44</v>
+        <v>10807.6</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22018.09</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2628.44</v>
+        <v>2638.7</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13264.39</v>
+        <v>13397.22</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1879.22</v>
+        <v>1888.8</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14286.17</v>
+        <v>14241.05</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5152.57</v>
+        <v>5142.24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1365,6 +1365,250 @@
         <v>5142.24</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1134432-566-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>9720.629999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1134432-587-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>3730.53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1134432-597-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>303.28</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1198-203-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>5193.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1607,6 +1607,677 @@
       </c>
       <c r="M19" s="2" t="n">
         <v>5193.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>838794-185-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.980.420-1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.345.484-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>6856.65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1134432-613-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2401.43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1422051-306-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>70.064.202-K</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EL PUENTE - MAQUINARIA Y CONSTRUCCION SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.411.861-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>40794.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1134432-647-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.850.715-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1440.51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2123-317-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>10096.61</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2427-833-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>7452.57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>836-153-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>72.235.100-2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL V REGION</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>75458.86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2427-826-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>6057.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>813685-229-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LUCANO RENT A CAR S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.813.177-5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>313.01</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3073-382-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.102.015-5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>10084.03</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2427-889-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>32577.09</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -623,7 +623,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>15.751.336-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1363,11 @@
           <t>77.854.171-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1855,11 @@
           <t>77.850.715-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2123-317-CM26</t>
+          <t>836-153-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10096.61</v>
+        <v>75458.86</v>
       </c>
     </row>
     <row r="25">
@@ -1994,7 +1994,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>836-153-CM26</t>
+          <t>2123-317-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>75458.86</v>
+        <v>10096.61</v>
       </c>
     </row>
     <row r="27">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2294,6 +2294,559 @@
       </c>
       <c r="M30" s="2" t="n">
         <v>32577.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1705-646-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.606.603-k</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>FEBGIP SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>5836.21</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1725-974-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>253.85</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1375753-176-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.981.290-5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>11845.69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1134432-689-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>2881.72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5035-117-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>14262.28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3249-148-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.102.049-k</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>2421.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2123-369-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1737.16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1134432-704-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>224.31</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1943-401-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>12163.23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2791,7 +2791,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1943-401-CM26</t>
+          <t>1134432-720-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2846,6 +2846,67 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
+        <v>510.95</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1943-401-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>12163.23</v>
       </c>
     </row>
